--- a/xlsx/Power/p1.xlsx
+++ b/xlsx/Power/p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EB5BE9-6D01-4861-9A0C-D1E6F7AF223D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B8C12E-9274-4A40-9A92-830C83D3A486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E15D2A45-245A-4B67-99D0-7B2747112454}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E15D2A45-245A-4B67-99D0-7B2747112454}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,16 +404,16 @@
         <v>0.85599999999999998</v>
       </c>
       <c r="C1">
-        <v>0.96499999999999997</v>
+        <v>0.85199999999999998</v>
       </c>
       <c r="D1">
-        <v>0.98499999999999999</v>
+        <v>0.96299999999999997</v>
       </c>
       <c r="E1">
-        <v>0.995</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="F1">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="G1">
         <v>0.999</v>
@@ -436,13 +436,13 @@
         <v>0.877</v>
       </c>
       <c r="C2">
-        <v>0.97499999999999998</v>
+        <v>0.877</v>
       </c>
       <c r="D2">
-        <v>0.99199999999999999</v>
+        <v>0.97099999999999997</v>
       </c>
       <c r="E2">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -468,7 +468,7 @@
         <v>0.873</v>
       </c>
       <c r="C3">
-        <v>0.96699999999999997</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="D3">
         <v>0.99299999999999999</v>
@@ -494,13 +494,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.64600000000000002</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="B4">
-        <v>0.873</v>
+        <v>0.876</v>
       </c>
       <c r="C4">
-        <v>0.96399999999999997</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="D4">
         <v>0.99199999999999999</v>
@@ -532,28 +532,28 @@
         <v>0.20200000000000001</v>
       </c>
       <c r="C5">
-        <v>0.26900000000000002</v>
+        <v>1E-3</v>
       </c>
       <c r="D5">
-        <v>0.38</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="E5">
-        <v>0.45500000000000002</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="F5">
-        <v>0.58399999999999996</v>
+        <v>0.221</v>
       </c>
       <c r="G5">
-        <v>0.68</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="H5">
-        <v>0.72699999999999998</v>
+        <v>0.47299999999999998</v>
       </c>
       <c r="I5">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="J5">
-        <v>0.86399999999999999</v>
+        <v>0.68200000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,13 +564,13 @@
         <v>0.85099999999999998</v>
       </c>
       <c r="C6">
-        <v>0.96699999999999997</v>
+        <v>0.97699999999999998</v>
       </c>
       <c r="D6">
-        <v>0.98199999999999998</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="E6">
-        <v>0.996</v>
+        <v>0.997</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -596,7 +596,7 @@
         <v>0.84299999999999997</v>
       </c>
       <c r="C7">
-        <v>0.95299999999999996</v>
+        <v>0.95</v>
       </c>
       <c r="D7">
         <v>0.97599999999999998</v>
@@ -628,25 +628,25 @@
         <v>0.754</v>
       </c>
       <c r="C8">
-        <v>0.91200000000000003</v>
+        <v>0.54600000000000004</v>
       </c>
       <c r="D8">
-        <v>0.97</v>
+        <v>0.89600000000000002</v>
       </c>
       <c r="E8">
-        <v>0.98299999999999998</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="F8">
-        <v>0.998</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="G8">
-        <v>0.996</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -660,19 +660,19 @@
         <v>0.63700000000000001</v>
       </c>
       <c r="C9">
-        <v>0.94399999999999995</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="D9">
-        <v>0.96399999999999997</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>0.97599999999999998</v>
+        <v>0.997</v>
       </c>
       <c r="F9">
-        <v>0.99099999999999999</v>
+        <v>0.998</v>
       </c>
       <c r="G9">
-        <v>0.99299999999999999</v>
+        <v>0.995</v>
       </c>
       <c r="H9">
         <v>0.998</v>
@@ -681,7 +681,7 @@
         <v>0.999</v>
       </c>
       <c r="J9">
-        <v>0.998</v>
+        <v>0.999</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p1.xlsx
+++ b/xlsx/Power/p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B8C12E-9274-4A40-9A92-830C83D3A486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEAD712-AEE7-45CA-8641-FA3277473572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E15D2A45-245A-4B67-99D0-7B2747112454}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E15D2A45-245A-4B67-99D0-7B2747112454}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,16 +404,16 @@
         <v>0.85599999999999998</v>
       </c>
       <c r="C1">
-        <v>0.85199999999999998</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="D1">
-        <v>0.96299999999999997</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="E1">
-        <v>0.98799999999999999</v>
+        <v>0.995</v>
       </c>
       <c r="F1">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="G1">
         <v>0.999</v>
@@ -436,13 +436,13 @@
         <v>0.877</v>
       </c>
       <c r="C2">
-        <v>0.877</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="D2">
-        <v>0.97099999999999997</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="E2">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -468,7 +468,7 @@
         <v>0.873</v>
       </c>
       <c r="C3">
-        <v>0.97199999999999998</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="D3">
         <v>0.99299999999999999</v>
@@ -494,13 +494,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.66700000000000004</v>
+        <v>0.64600000000000002</v>
       </c>
       <c r="B4">
-        <v>0.876</v>
+        <v>0.873</v>
       </c>
       <c r="C4">
-        <v>0.96499999999999997</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="D4">
         <v>0.99199999999999999</v>
@@ -532,28 +532,28 @@
         <v>0.20200000000000001</v>
       </c>
       <c r="C5">
-        <v>1E-3</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="D5">
-        <v>3.5999999999999997E-2</v>
+        <v>0.379</v>
       </c>
       <c r="E5">
-        <v>9.7000000000000003E-2</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="F5">
-        <v>0.221</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="G5">
-        <v>0.34100000000000003</v>
+        <v>0.68</v>
       </c>
       <c r="H5">
-        <v>0.47299999999999998</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="I5">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="J5">
-        <v>0.68200000000000005</v>
+        <v>0.86399999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,13 +564,13 @@
         <v>0.85099999999999998</v>
       </c>
       <c r="C6">
-        <v>0.97699999999999998</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="D6">
-        <v>0.98799999999999999</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="E6">
-        <v>0.997</v>
+        <v>0.996</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -596,7 +596,7 @@
         <v>0.84299999999999997</v>
       </c>
       <c r="C7">
-        <v>0.95</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="D7">
         <v>0.97599999999999998</v>
@@ -628,25 +628,25 @@
         <v>0.754</v>
       </c>
       <c r="C8">
-        <v>0.54600000000000004</v>
+        <v>0.91200000000000003</v>
       </c>
       <c r="D8">
-        <v>0.89600000000000002</v>
+        <v>0.97</v>
       </c>
       <c r="E8">
-        <v>0.96799999999999997</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="F8">
-        <v>0.99199999999999999</v>
+        <v>0.998</v>
       </c>
       <c r="G8">
-        <v>0.99199999999999999</v>
+        <v>0.996</v>
       </c>
       <c r="H8">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -660,19 +660,19 @@
         <v>0.63700000000000001</v>
       </c>
       <c r="C9">
-        <v>0.98299999999999998</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="E9">
-        <v>0.997</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F9">
-        <v>0.998</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="G9">
-        <v>0.995</v>
+        <v>0.99299999999999999</v>
       </c>
       <c r="H9">
         <v>0.998</v>
@@ -681,7 +681,7 @@
         <v>0.999</v>
       </c>
       <c r="J9">
-        <v>0.999</v>
+        <v>0.998</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p1.xlsx
+++ b/xlsx/Power/p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEAD712-AEE7-45CA-8641-FA3277473572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9717D240-7423-40A8-9307-EAC3FBEADDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E15D2A45-245A-4B67-99D0-7B2747112454}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E15D2A45-245A-4B67-99D0-7B2747112454}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="165" formatCode="#,##0.000_ ;[Red]\-#,##0.000\ "/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -68,8 +72,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -393,12 +399,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D71C96E8-0971-46C2-A8D4-C8548153DBD2}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.60699999999999998</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="B1">
         <v>0.85599999999999998</v>
@@ -427,10 +433,19 @@
       <c r="J1">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.64700000000000002</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="B2">
         <v>0.877</v>
@@ -459,8 +474,17 @@
       <c r="J2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.63800000000000001</v>
       </c>
@@ -468,7 +492,7 @@
         <v>0.873</v>
       </c>
       <c r="C3">
-        <v>0.96699999999999997</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="D3">
         <v>0.99299999999999999</v>
@@ -491,13 +515,22 @@
       <c r="J3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.64600000000000002</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="B4">
-        <v>0.873</v>
+        <v>0.876</v>
       </c>
       <c r="C4">
         <v>0.96399999999999997</v>
@@ -523,42 +556,60 @@
       <c r="J4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.14199999999999999</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="B5">
-        <v>0.20200000000000001</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="C5">
-        <v>0.26900000000000002</v>
+        <v>0.745</v>
       </c>
       <c r="D5">
-        <v>0.379</v>
+        <v>0.86399999999999999</v>
       </c>
       <c r="E5">
-        <v>0.45500000000000002</v>
+        <v>0.91900000000000004</v>
       </c>
       <c r="F5">
-        <v>0.58399999999999996</v>
+        <v>0.95699999999999996</v>
       </c>
       <c r="G5">
-        <v>0.68</v>
+        <v>0.97699999999999998</v>
       </c>
       <c r="H5">
-        <v>0.72699999999999998</v>
+        <v>0.995</v>
       </c>
       <c r="I5">
-        <v>0.8</v>
+        <v>0.998</v>
       </c>
       <c r="J5">
-        <v>0.86399999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.999</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.60599999999999998</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="B6">
         <v>0.85099999999999998</v>
@@ -587,16 +638,25 @@
       <c r="J6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.6</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="B7">
-        <v>0.84299999999999997</v>
+        <v>0.84199999999999997</v>
       </c>
       <c r="C7">
-        <v>0.95299999999999996</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="D7">
         <v>0.97599999999999998</v>
@@ -619,8 +679,17 @@
       <c r="J7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0.433</v>
       </c>
@@ -634,7 +703,7 @@
         <v>0.97</v>
       </c>
       <c r="E8">
-        <v>0.98299999999999998</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="F8">
         <v>0.998</v>
@@ -651,13 +720,22 @@
       <c r="J8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.51300000000000001</v>
       </c>
       <c r="B9">
-        <v>0.63700000000000001</v>
+        <v>0.64100000000000001</v>
       </c>
       <c r="C9">
         <v>0.94399999999999995</v>
@@ -666,7 +744,7 @@
         <v>0.96399999999999997</v>
       </c>
       <c r="E9">
-        <v>0.97599999999999998</v>
+        <v>0.97399999999999998</v>
       </c>
       <c r="F9">
         <v>0.99099999999999999</v>
@@ -683,8 +761,225 @@
       <c r="J9">
         <v>0.998</v>
       </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>